--- a/statistika_vkr.xlsx
+++ b/statistika_vkr.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="22527"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d79c6ec1d0c7b0c7/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_AD4DF75460589B3ACB72846C875860925ADEDD80" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{C8F97514-1575-4819-9B43-BC5F0D22CA8C}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6A6BE314-D1F1-4461-8D2F-D513911BDA58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -20,26 +20,14 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
   <si>
     <t>Год</t>
-  </si>
-  <si>
-    <t>1,2 млн</t>
-  </si>
-  <si>
-    <t>1,8 млн</t>
   </si>
   <si>
     <t>Количество электронных документов (млн.)</t>
@@ -438,16 +426,16 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
@@ -559,8 +547,8 @@
       <c r="B8" s="3">
         <v>55</v>
       </c>
-      <c r="C8" s="3" t="s">
-        <v>1</v>
+      <c r="C8" s="3">
+        <v>1.2</v>
       </c>
       <c r="D8" s="3">
         <v>6</v>
@@ -576,8 +564,8 @@
       <c r="B9" s="3">
         <v>75.2</v>
       </c>
-      <c r="C9" s="3" t="s">
-        <v>2</v>
+      <c r="C9" s="3">
+        <v>1.8</v>
       </c>
       <c r="D9" s="3">
         <v>7.2</v>
